--- a/improvement/realestate/plan-07.xlsx
+++ b/improvement/realestate/plan-07.xlsx
@@ -622,7 +622,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>500万円（従業員5人以下・カタログ注文型。特例750万円）</t>
+          <t>従業員6〜20人は500万円（賃上げ要件達成で750万円）。5人以下は200万円（300万円）、21人以上は1,000万円（1,500万円）</t>
         </is>
       </c>
     </row>
